--- a/outputs/daily/hr_rankings_2026-06-21.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-21.xlsx
@@ -4928,7 +4928,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9075,27 +9075,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>669065</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9105,17 +9105,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9138,26 +9138,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>30.7</v>
+        <v>32</v>
       </c>
       <c r="R32" t="n">
-        <v>54.9</v>
+        <v>35</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>54.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9214,22 +9214,22 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9239,112 +9239,112 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>102.4017</t>
+          <t>102.6403</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4813</t>
+          <t>0.4572</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.2203</t>
+          <t>0.2153</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3407</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.93</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>48.54</t>
+          <t>49.88</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.2021</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.3738</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9355,47 +9355,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9418,26 +9418,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>33.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>51.6</v>
+        <v>30.7</v>
       </c>
       <c r="R33" t="n">
-        <v>60.2</v>
+        <v>54.9</v>
       </c>
       <c r="S33" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T33" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>43.9</v>
+        <v>54.7</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9489,27 +9489,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/31, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9519,112 +9519,112 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>99.5306</t>
+          <t>102.4017</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.4813</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.2203</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3276</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>48.54</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4699</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9635,32 +9635,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9698,17 +9698,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>57.1</v>
+        <v>33.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>42</v>
+        <v>51.6</v>
       </c>
       <c r="R34" t="n">
-        <v>35.6</v>
+        <v>60.2</v>
       </c>
       <c r="S34" t="n">
         <v>94.90000000000001</v>
@@ -9717,7 +9717,7 @@
         <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>7</v>
+        <v>43.9</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9769,27 +9769,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 9/31, 1 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9799,97 +9799,97 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>90.88</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>102.6039</t>
+          <t>99.5306</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4602</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.3276</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>75.46</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4111</t>
+          <t>0.4699</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9915,47 +9915,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>663457</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-21T18:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Stephen Kolek</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>663568</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9978,26 +9978,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>60.5</v>
+        <v>57.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>31.7</v>
+        <v>42</v>
       </c>
       <c r="R35" t="n">
-        <v>45.7</v>
+        <v>35.6</v>
       </c>
       <c r="S35" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T35" t="n">
         <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>27.7</v>
+        <v>7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10064,117 +10064,117 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>55.32</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>90.88</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>102.1345</t>
+          <t>102.6039</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4812</t>
+          <t>0.4602</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2243</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>74.03</t>
+          <t>75.46</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.4111</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1215</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10195,47 +10195,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>663457</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-21T20:05:00Z</t>
+          <t>2026-06-21T18:10:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jack Perkins</t>
+          <t>Stephen Kolek</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>678022</t>
+          <t>663568</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10258,26 +10258,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>50.5</v>
+        <v>60.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>30.2</v>
+        <v>31.7</v>
       </c>
       <c r="R36" t="n">
-        <v>68.40000000000001</v>
+        <v>45.7</v>
       </c>
       <c r="S36" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>68</v>
+        <v>27.7</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10329,142 +10329,142 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>55.32</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>99.9843</t>
+          <t>102.1345</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.4812</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.2209</t>
+          <t>0.2243</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3272</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>74.03</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>49.51</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.2226</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1215</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10475,27 +10475,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T20:05:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10505,17 +10505,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>678022</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10538,26 +10538,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>41.4</v>
+        <v>50.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>54.9</v>
+        <v>30.2</v>
       </c>
       <c r="R37" t="n">
-        <v>44.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S37" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T37" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>46.4</v>
+        <v>68</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10609,142 +10609,142 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.3517</t>
+          <t>99.9843</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.2209</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3272</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>75.22</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>49.51</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.2226</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.4041</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10755,32 +10755,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10822,13 +10822,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>59.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>30.7</v>
+        <v>54.9</v>
       </c>
       <c r="R38" t="n">
-        <v>54.9</v>
+        <v>44.4</v>
       </c>
       <c r="S38" t="n">
         <v>86.40000000000001</v>
@@ -10837,7 +10837,7 @@
         <v>80</v>
       </c>
       <c r="U38" t="n">
-        <v>7</v>
+        <v>46.4</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10889,142 +10889,142 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>13.49</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>51.55</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>92.33</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>103.2106</t>
+          <t>102.3517</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4626</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.2153</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3575</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>76.78</t>
+          <t>75.22</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.2109</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.4041</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -11035,27 +11035,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -11065,17 +11065,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -11098,26 +11098,26 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>54.4</v>
+        <v>59.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>42</v>
+        <v>30.7</v>
       </c>
       <c r="R39" t="n">
-        <v>35.6</v>
+        <v>54.9</v>
       </c>
       <c r="S39" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T39" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U39" t="n">
-        <v>62.8</v>
+        <v>7</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -11169,142 +11169,142 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>13.49</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>48.36</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>92.33</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>101.468</t>
+          <t>103.2106</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.5338</t>
+          <t>0.4626</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.2382</t>
+          <t>0.2153</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.3832</t>
+          <t>0.3575</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>76.78</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.2331</t>
+          <t>0.2109</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.4111</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr"/>
@@ -11315,32 +11315,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -11364,7 +11364,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>54.8</v>
+        <v>55</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -11378,26 +11378,26 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>27.2</v>
+        <v>54.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="R40" t="n">
-        <v>60.2</v>
+        <v>35.6</v>
       </c>
       <c r="S40" t="n">
         <v>100</v>
       </c>
       <c r="T40" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U40" t="n">
-        <v>70.8</v>
+        <v>62.8</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -11449,27 +11449,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -11479,97 +11479,97 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>48.36</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>99.923</t>
+          <t>101.468</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.5338</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.2382</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3832</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.2331</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.4111</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr"/>
@@ -11595,32 +11595,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>643217</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Keider Montero</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>672456</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>54.6</v>
+        <v>54.8</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11658,26 +11658,26 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>43.8</v>
+        <v>27.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>43.3</v>
+        <v>52</v>
       </c>
       <c r="R41" t="n">
-        <v>35.6</v>
+        <v>60.2</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
       </c>
       <c r="T41" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U41" t="n">
-        <v>64.8</v>
+        <v>70.8</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -11729,12 +11729,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -11759,97 +11759,97 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>98.9804</t>
+          <t>99.923</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>0.4342</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>69.33</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.1931</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr"/>
@@ -11875,47 +11875,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>676475</t>
+          <t>643217</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-21T18:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Stephen Kolek</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>663568</t>
+          <t>672456</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -11924,7 +11924,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -11942,22 +11942,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>53.9</v>
+        <v>43.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>31.7</v>
+        <v>43.3</v>
       </c>
       <c r="R42" t="n">
-        <v>45.7</v>
+        <v>35.6</v>
       </c>
       <c r="S42" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T42" t="n">
         <v>80</v>
       </c>
       <c r="U42" t="n">
-        <v>31.4</v>
+        <v>64.8</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -12009,27 +12009,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -12039,102 +12039,102 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>101.6192</t>
+          <t>98.9804</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>0.4342</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.2389</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3744</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.33</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1921</t>
+          <t>0.1931</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.1215</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12155,27 +12155,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>669065</t>
+          <t>676475</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T18:10:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -12185,17 +12185,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Stephen Kolek</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>663568</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12222,22 +12222,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>55.5</v>
+        <v>53.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="R43" t="n">
-        <v>35</v>
+        <v>45.7</v>
       </c>
       <c r="S43" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T43" t="n">
         <v>80</v>
       </c>
       <c r="U43" t="n">
-        <v>52.8</v>
+        <v>31.4</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -12289,27 +12289,27 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 1 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -12319,112 +12319,112 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>51.44</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>102.6403</t>
+          <t>101.6192</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.4572</t>
+          <t>0.527</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.2153</t>
+          <t>0.2389</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.3407</t>
+          <t>0.3744</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>74.93</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>49.88</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.2021</t>
+          <t>0.1921</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.3738</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1215</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -22812,7 +22812,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -25588,7 +25588,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -29224,7 +29224,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>80</v>
       </c>
       <c r="U104" t="n">
-        <v>63.7</v>
+        <v>61.5</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -30600,7 +30600,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -37032,7 +37032,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -39828,7 +39828,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -46764,7 +46764,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -48156,7 +48156,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -54804,7 +54804,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -55364,7 +55364,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -58111,27 +58111,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>682622</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Noelvi Marte</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -58146,12 +58146,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Elmer Rodríguez</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>695684</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -58160,7 +58160,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -58178,13 +58178,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>24.1</v>
+        <v>26.6</v>
       </c>
       <c r="Q208" t="n">
-        <v>32</v>
+        <v>17.3</v>
       </c>
       <c r="R208" t="n">
-        <v>35</v>
+        <v>50.7</v>
       </c>
       <c r="S208" t="n">
         <v>64.3</v>
@@ -58193,7 +58193,7 @@
         <v>50</v>
       </c>
       <c r="U208" t="n">
-        <v>63.3</v>
+        <v>68.3</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
       <c r="AB208" t="inlineStr"/>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr"/>
@@ -58245,27 +58245,27 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Contact streak: 6/14 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.3% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -58275,112 +58275,112 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>32.31</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>96.5176</t>
+          <t>99.2676</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.3781</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.1582</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.2889</t>
+          <t>0.2844</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.2529</t>
+          <t>0.1808</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.3738</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH208" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -58391,27 +58391,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>682622</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -58426,12 +58426,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Elmer Rodríguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>695684</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -58458,13 +58458,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>26.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>17.3</v>
+        <v>32</v>
       </c>
       <c r="R209" t="n">
-        <v>50.7</v>
+        <v>35</v>
       </c>
       <c r="S209" t="n">
         <v>64.3</v>
@@ -58473,7 +58473,7 @@
         <v>50</v>
       </c>
       <c r="U209" t="n">
-        <v>68.3</v>
+        <v>60.3</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
@@ -58508,7 +58508,7 @@
       <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr"/>
@@ -58525,27 +58525,27 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 6/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.3% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -58555,112 +58555,112 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>99.2676</t>
+          <t>96.5176</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3781</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.1582</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.2844</t>
+          <t>0.2889</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.1808</t>
+          <t>0.2529</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3738</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH209" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -60656,7 +60656,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -61192,7 +61192,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -61752,7 +61752,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -64934,7 +64934,7 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
@@ -64944,7 +64944,7 @@
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/13, 0 HR</t>
+          <t>Last 7 games: 1/14, 0 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
@@ -65075,32 +65075,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -65110,21 +65110,21 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>672456</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L233" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -65142,13 +65142,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>24.6</v>
+        <v>14.5</v>
       </c>
       <c r="Q233" t="n">
-        <v>24.8</v>
+        <v>43.3</v>
       </c>
       <c r="R233" t="n">
-        <v>44.4</v>
+        <v>35.6</v>
       </c>
       <c r="S233" t="n">
         <v>44.8</v>
@@ -65157,7 +65157,7 @@
         <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>29.2</v>
+        <v>35.6</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -65214,22 +65214,22 @@
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Contact streak: 5/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
@@ -65239,112 +65239,112 @@
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>98.7983</t>
+          <t>99.6106</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.0637</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.2675</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.1052</t>
+          <t>0.0232</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH233" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI233" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ233" t="inlineStr"/>
@@ -65355,32 +65355,32 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>673490</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ha-Seong Kim</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -65390,12 +65390,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -65404,7 +65404,7 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -65418,26 +65418,26 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P234" t="n">
-        <v>9.300000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="Q234" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="R234" t="n">
-        <v>54.9</v>
+        <v>44.4</v>
       </c>
       <c r="S234" t="n">
         <v>44.8</v>
       </c>
       <c r="T234" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U234" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -65489,142 +65489,142 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/10, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 4.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>95.6299</t>
+          <t>98.7983</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.0657</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.2382</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>71.55</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.0333</t>
+          <t>0.1052</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="BE234" t="inlineStr">
         <is>
-          <t>0.1628</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH234" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -65635,27 +65635,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>673490</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Ha-Seong Kim</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -65670,17 +65670,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Keider Montero</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>672456</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L235" t="n">
@@ -65698,26 +65698,26 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>14.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q235" t="n">
-        <v>43.3</v>
+        <v>34.4</v>
       </c>
       <c r="R235" t="n">
-        <v>35.6</v>
+        <v>54.9</v>
       </c>
       <c r="S235" t="n">
         <v>44.8</v>
       </c>
       <c r="T235" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U235" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -65769,12 +65769,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -65784,127 +65784,127 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Contact streak: 5/15 over last 7 games</t>
+          <t>Last 7 games: 0/10, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 4.5 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>99.6106</t>
+          <t>95.6299</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.0637</t>
+          <t>0.0657</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.2675</t>
+          <t>0.2382</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>71.55</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.0232</t>
+          <t>0.0333</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE235" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1628</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH235" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -67422,7 +67422,7 @@
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AJ241" t="inlineStr">
@@ -67432,7 +67432,7 @@
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Last 2 games: 0/3, 0 HR</t>
+          <t>Last 2 games: 0/4, 0 HR</t>
         </is>
       </c>
       <c r="AL241" t="inlineStr">
@@ -75414,7 +75414,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-06-21.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-21.xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1657,7 +1657,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>66.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1709,22 +1709,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3593,7 +3593,7 @@
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -4911,27 +4911,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4974,26 +4974,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>27.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>54.9</v>
       </c>
       <c r="R17" t="n">
-        <v>66.7</v>
+        <v>56.4</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5028,7 +5028,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5045,27 +5045,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5075,112 +5075,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.923</t>
+          <t>102.3517</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>75.22</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.4041</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5191,47 +5191,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5254,26 +5254,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>41.4</v>
+        <v>33.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.9</v>
+        <v>51.6</v>
       </c>
       <c r="R18" t="n">
-        <v>56.4</v>
+        <v>66.7</v>
       </c>
       <c r="S18" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>34.2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5355,112 +5355,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.3517</t>
+          <t>99.5306</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3276</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>75.22</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4041</t>
+          <t>0.4699</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5471,24 +5471,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-06-21T19:10:00Z</t>
@@ -5496,22 +5496,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5534,26 +5534,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>33.7</v>
+        <v>27.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="R19" t="n">
         <v>66.7</v>
       </c>
       <c r="S19" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>34.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5588,7 +5588,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5605,27 +5605,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5635,97 +5635,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.5306</t>
+          <t>99.923</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3276</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4699</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>78</v>
       </c>
       <c r="U32" t="n">
-        <v>78.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -10203,22 +10203,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -10266,26 +10266,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>33.4</v>
+        <v>47.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>42.1</v>
+        <v>24.8</v>
       </c>
       <c r="R36" t="n">
-        <v>61.6</v>
+        <v>56.4</v>
       </c>
       <c r="S36" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>72.7</v>
+        <v>25.3</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10337,142 +10337,142 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>89.59</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>98.2946</t>
+          <t>102.8449</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4318</t>
+          <t>0.4685</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.2034</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3419</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>76.54</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1711</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4215</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1707</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10483,22 +10483,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Julio Rodríguez</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10513,26 +10513,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10546,26 +10546,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>47.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.8</v>
+        <v>42.1</v>
       </c>
       <c r="R37" t="n">
-        <v>56.4</v>
+        <v>61.6</v>
       </c>
       <c r="S37" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T37" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>25.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10617,27 +10617,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10647,112 +10647,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.8449</t>
+          <t>100.4685</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4685</t>
+          <t>0.4539</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3419</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>76.54</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>28.37</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.4215</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1707</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -10826,11 +10826,11 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>40.6</v>
+        <v>33.4</v>
       </c>
       <c r="Q38" t="n">
         <v>42.1</v>
@@ -10839,13 +10839,13 @@
         <v>61.6</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T38" t="n">
         <v>50</v>
       </c>
       <c r="U38" t="n">
-        <v>8.800000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -10897,22 +10897,22 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -10922,37 +10922,37 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>89.59</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>100.4685</t>
+          <t>98.2946</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4539</t>
+          <t>0.4318</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
@@ -10962,32 +10962,32 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.1711</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -26397,7 +26397,7 @@
         <v>78</v>
       </c>
       <c r="U94" t="n">
-        <v>40.7</v>
+        <v>39.2</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -26464,7 +26464,7 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 7/27, 1 HR</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
@@ -26620,7 +26620,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -31906,7 +31906,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -31939,7 +31939,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>66.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -31991,22 +31991,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -32442,7 +32442,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -33875,7 +33875,7 @@
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -35193,27 +35193,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -35223,17 +35223,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -35256,26 +35256,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>27.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>54.9</v>
       </c>
       <c r="R17" t="n">
-        <v>66.7</v>
+        <v>56.4</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -35310,7 +35310,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -35327,27 +35327,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -35357,112 +35357,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.923</t>
+          <t>102.3517</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>75.22</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.4041</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -35473,47 +35473,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -35536,26 +35536,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>41.4</v>
+        <v>33.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.9</v>
+        <v>51.6</v>
       </c>
       <c r="R18" t="n">
-        <v>56.4</v>
+        <v>66.7</v>
       </c>
       <c r="S18" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>34.2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -35607,12 +35607,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -35622,12 +35622,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -35637,112 +35637,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.3517</t>
+          <t>99.5306</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3276</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>75.22</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4041</t>
+          <t>0.4699</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -35753,24 +35753,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-06-21T19:10:00Z</t>
@@ -35778,22 +35778,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -35816,26 +35816,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>33.7</v>
+        <v>27.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="R19" t="n">
         <v>66.7</v>
       </c>
       <c r="S19" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>34.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -35870,7 +35870,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -35887,27 +35887,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -35917,97 +35917,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.5306</t>
+          <t>99.923</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3276</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4699</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
